--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4759" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5555" uniqueCount="727">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1113,6 +1113,75 @@
     <t>http://example.org/ValueSet/moped-behandlungsart-valueset</t>
   </si>
   <si>
+    <t>Encounter.class:Behandlungsart.id</t>
+  </si>
+  <si>
+    <t>Encounter.class.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.system</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.system</t>
+  </si>
+  <si>
+    <t>http://tbd.at/MOPED-encounter-behandlungsart</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.code</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.code</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.text</t>
+  </si>
+  <si>
+    <t>Encounter.class.text</t>
+  </si>
+  <si>
     <t>Encounter.class:Aufnahmeart</t>
   </si>
   <si>
@@ -1120,6 +1189,42 @@
   </si>
   <si>
     <t>http://example.org/ValueSet/moped-aufnahmeart-valueset</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.system</t>
+  </si>
+  <si>
+    <t>http://tbd.at/moped-ext-aufnahmeart</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.code</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.text</t>
   </si>
   <si>
     <t>Encounter.priority</t>
@@ -2483,7 +2588,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN132"/>
+  <dimension ref="A1:AN154"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.9453125" customWidth="true" bestFit="true"/>
@@ -8802,11 +8907,9 @@
         <v>355</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C56" t="s" s="2">
         <v>356</v>
       </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>20</v>
       </c>
@@ -8824,16 +8927,16 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>356</v>
+        <v>167</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>344</v>
+        <v>168</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8860,11 +8963,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -8882,50 +8987,50 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>342</v>
+        <v>169</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>350</v>
+        <v>171</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8937,15 +9042,17 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>359</v>
+        <v>174</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8970,63 +9077,63 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>358</v>
+        <v>177</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>364</v>
+        <v>171</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>365</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9049,18 +9156,20 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>367</v>
+        <v>205</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>368</v>
+        <v>206</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -9084,13 +9193,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -9108,7 +9217,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>366</v>
+        <v>209</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9123,24 +9232,24 @@
         <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>374</v>
+        <v>210</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>375</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9151,7 +9260,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9160,16 +9269,16 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>377</v>
+        <v>90</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>378</v>
+        <v>167</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>379</v>
+        <v>168</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9196,13 +9305,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9220,22 +9329,22 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>376</v>
+        <v>169</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>372</v>
+        <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>20</v>
@@ -9244,26 +9353,26 @@
         <v>171</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>382</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>384</v>
+        <v>148</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9272,19 +9381,19 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>385</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>386</v>
+        <v>174</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>387</v>
+        <v>175</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>388</v>
+        <v>151</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9322,51 +9431,51 @@
         <v>20</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>383</v>
+        <v>177</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>389</v>
+        <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>391</v>
+        <v>171</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>392</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9374,7 +9483,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>88</v>
@@ -9386,21 +9495,23 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>394</v>
+        <v>218</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>395</v>
+        <v>219</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
       </c>
@@ -9409,7 +9520,7 @@
         <v>20</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>20</v>
+        <v>367</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>20</v>
@@ -9424,13 +9535,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>398</v>
+        <v>20</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9448,7 +9559,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>393</v>
+        <v>222</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9469,18 +9580,18 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9491,7 +9602,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9503,15 +9614,17 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>400</v>
+        <v>227</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>401</v>
+        <v>228</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9560,13 +9673,13 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>399</v>
+        <v>231</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
@@ -9578,32 +9691,32 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>404</v>
+        <v>233</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9612,19 +9725,21 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>407</v>
+        <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>408</v>
+        <v>236</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>409</v>
+        <v>237</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
@@ -9672,39 +9787,39 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>405</v>
+        <v>240</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>411</v>
+        <v>242</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>373</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9715,7 +9830,7 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9724,19 +9839,21 @@
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>413</v>
+        <v>227</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>246</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>247</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
@@ -9784,16 +9901,16 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>249</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>100</v>
@@ -9805,18 +9922,18 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>416</v>
+        <v>374</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>416</v>
+        <v>375</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9836,21 +9953,23 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>417</v>
+        <v>254</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>418</v>
+        <v>255</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>419</v>
+        <v>256</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
       </c>
@@ -9898,7 +10017,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>259</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9913,24 +10032,24 @@
         <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>422</v>
+        <v>260</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>423</v>
+        <v>377</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9950,19 +10069,23 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>424</v>
+        <v>227</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>425</v>
+        <v>264</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
       </c>
@@ -10010,7 +10133,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>423</v>
+        <v>268</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10025,26 +10148,28 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>428</v>
+        <v>269</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>429</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>430</v>
+        <v>378</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>20</v>
       </c>
@@ -10053,7 +10178,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -10065,17 +10190,15 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>431</v>
+        <v>190</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10100,13 +10223,11 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -10124,7 +10245,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>430</v>
+        <v>342</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10136,27 +10257,27 @@
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>435</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>436</v>
+        <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>437</v>
+        <v>350</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>438</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>439</v>
+        <v>381</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>439</v>
+        <v>356</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10179,7 +10300,7 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>227</v>
+        <v>90</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>167</v>
@@ -10265,10 +10386,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>440</v>
+        <v>358</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10338,16 +10459,16 @@
         <v>20</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>177</v>
@@ -10379,14 +10500,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>441</v>
+        <v>383</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>360</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10399,25 +10520,25 @@
         <v>20</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
+        <v>205</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>444</v>
+        <v>206</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10466,7 +10587,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>445</v>
+        <v>209</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10478,7 +10599,7 @@
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -10487,18 +10608,18 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>20</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>446</v>
+        <v>384</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>446</v>
+        <v>362</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10509,7 +10630,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
@@ -10518,20 +10639,18 @@
         <v>20</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>447</v>
+        <v>167</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10556,13 +10675,13 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>450</v>
+        <v>20</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>448</v>
+        <v>20</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>451</v>
+        <v>20</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -10580,50 +10699,50 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>446</v>
+        <v>169</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>452</v>
+        <v>170</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>454</v>
+        <v>171</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>455</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>456</v>
+        <v>385</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>456</v>
+        <v>364</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -10635,15 +10754,17 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>293</v>
+        <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>457</v>
+        <v>174</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10680,31 +10801,31 @@
         <v>20</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>456</v>
+        <v>177</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -10713,18 +10834,18 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>459</v>
+        <v>171</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>460</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>461</v>
+        <v>386</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>461</v>
+        <v>366</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10732,7 +10853,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>88</v>
@@ -10747,18 +10868,20 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>462</v>
+        <v>102</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>463</v>
+        <v>218</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>464</v>
+        <v>219</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
       </c>
@@ -10767,7 +10890,7 @@
         <v>20</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>20</v>
@@ -10806,7 +10929,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>461</v>
+        <v>222</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10815,30 +10938,30 @@
         <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>452</v>
+        <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>466</v>
+        <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>467</v>
+        <v>223</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>468</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>469</v>
+        <v>388</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>469</v>
+        <v>369</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10849,7 +10972,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -10861,15 +10984,17 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>470</v>
+        <v>227</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>471</v>
+        <v>228</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10918,13 +11043,13 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>469</v>
+        <v>231</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
@@ -10933,24 +11058,24 @@
         <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>473</v>
+        <v>232</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>474</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>389</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>475</v>
+        <v>371</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10961,7 +11086,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -10970,21 +11095,21 @@
         <v>20</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>476</v>
+        <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>477</v>
+        <v>236</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
       </c>
@@ -11032,16 +11157,16 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>475</v>
+        <v>240</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>100</v>
@@ -11053,18 +11178,18 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>480</v>
+        <v>373</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11084,21 +11209,21 @@
         <v>20</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>293</v>
+        <v>227</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>481</v>
+        <v>246</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
       </c>
@@ -11146,7 +11271,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>480</v>
+        <v>249</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11155,30 +11280,30 @@
         <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>484</v>
+        <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>485</v>
+        <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>486</v>
+        <v>250</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>487</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>488</v>
+        <v>391</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
+        <v>375</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11198,19 +11323,23 @@
         <v>20</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>489</v>
+        <v>254</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>490</v>
+        <v>255</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
       </c>
@@ -11258,7 +11387,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>488</v>
+        <v>259</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11279,18 +11408,18 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>492</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>493</v>
+        <v>392</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>493</v>
+        <v>377</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11310,19 +11439,23 @@
         <v>20</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>489</v>
+        <v>227</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>494</v>
+        <v>264</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
       </c>
@@ -11370,7 +11503,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>493</v>
+        <v>268</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11391,18 +11524,18 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>20</v>
+        <v>269</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>496</v>
+        <v>270</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>497</v>
+        <v>393</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>497</v>
+        <v>393</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11425,17 +11558,15 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>498</v>
+        <v>190</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>499</v>
+        <v>394</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11460,13 +11591,13 @@
         <v>20</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>20</v>
+        <v>395</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>20</v>
+        <v>397</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
@@ -11484,7 +11615,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>497</v>
+        <v>393</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11499,24 +11630,24 @@
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>484</v>
+        <v>20</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>20</v>
+        <v>398</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>502</v>
+        <v>399</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>503</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>504</v>
+        <v>401</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>504</v>
+        <v>401</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11539,16 +11670,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>431</v>
+        <v>190</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>505</v>
+        <v>402</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>506</v>
+        <v>403</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>507</v>
+        <v>404</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11574,29 +11705,31 @@
         <v>20</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>20</v>
+        <v>405</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>20</v>
+        <v>406</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AC80" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>504</v>
+        <v>401</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11611,24 +11744,24 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>20</v>
+        <v>407</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>20</v>
+        <v>409</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>20</v>
+        <v>410</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>509</v>
+        <v>411</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>509</v>
+        <v>411</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11639,7 +11772,7 @@
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -11648,16 +11781,16 @@
         <v>20</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>227</v>
+        <v>412</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>167</v>
+        <v>413</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>168</v>
+        <v>414</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11684,13 +11817,13 @@
         <v>20</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>20</v>
+        <v>415</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -11708,22 +11841,22 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>169</v>
+        <v>411</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>20</v>
+        <v>407</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>20</v>
@@ -11732,26 +11865,26 @@
         <v>171</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>20</v>
+        <v>417</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>510</v>
+        <v>418</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>510</v>
+        <v>418</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>148</v>
+        <v>419</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -11760,19 +11893,19 @@
         <v>20</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>135</v>
+        <v>420</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>174</v>
+        <v>421</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>175</v>
+        <v>422</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>151</v>
+        <v>423</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11822,75 +11955,73 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>177</v>
+        <v>418</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>171</v>
+        <v>426</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>20</v>
+        <v>427</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>511</v>
+        <v>428</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>511</v>
+        <v>428</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>20</v>
       </c>
@@ -11914,13 +12045,13 @@
         <v>20</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -11938,19 +12069,19 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>20</v>
@@ -11959,7 +12090,7 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>20</v>
@@ -11967,10 +12098,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>512</v>
+        <v>434</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>512</v>
+        <v>434</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11993,13 +12124,13 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>190</v>
+        <v>435</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>513</v>
+        <v>436</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>514</v>
+        <v>437</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12026,11 +12157,13 @@
         <v>20</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>515</v>
+        <v>20</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -12048,7 +12181,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>512</v>
+        <v>434</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12066,25 +12199,25 @@
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>20</v>
+        <v>438</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>20</v>
+        <v>439</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>516</v>
+        <v>440</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>516</v>
+        <v>440</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>517</v>
+        <v>441</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12100,16 +12233,16 @@
         <v>20</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>518</v>
+        <v>442</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>519</v>
+        <v>443</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>520</v>
+        <v>444</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12136,13 +12269,13 @@
         <v>20</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>522</v>
+        <v>20</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>20</v>
@@ -12160,7 +12293,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>516</v>
+        <v>440</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12175,28 +12308,26 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>523</v>
+        <v>445</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>524</v>
+        <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>525</v>
+        <v>446</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>526</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>527</v>
+        <v>447</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>20</v>
       </c>
@@ -12205,7 +12336,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>20</v>
@@ -12214,20 +12345,18 @@
         <v>20</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>529</v>
+        <v>449</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12276,7 +12405,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>504</v>
+        <v>447</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12297,7 +12426,7 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>20</v>
@@ -12305,10 +12434,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>530</v>
+        <v>451</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>509</v>
+        <v>451</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12331,15 +12460,17 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>227</v>
+        <v>452</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>167</v>
+        <v>453</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12388,7 +12519,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>169</v>
+        <v>451</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12397,19 +12528,19 @@
         <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>171</v>
+        <v>457</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>20</v>
@@ -12417,21 +12548,21 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>531</v>
+        <v>458</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>510</v>
+        <v>458</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>20</v>
@@ -12443,17 +12574,15 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>135</v>
+        <v>459</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>174</v>
+        <v>460</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12502,43 +12631,43 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>177</v>
+        <v>458</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>20</v>
+        <v>462</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>171</v>
+        <v>463</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>20</v>
+        <v>464</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>532</v>
+        <v>465</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>511</v>
+        <v>465</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12551,26 +12680,24 @@
         <v>20</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>135</v>
+        <v>466</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>20</v>
       </c>
@@ -12618,7 +12745,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12630,27 +12757,27 @@
         <v>20</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>141</v>
+        <v>470</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>20</v>
+        <v>471</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>133</v>
+        <v>472</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>20</v>
+        <v>473</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>533</v>
+        <v>474</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>512</v>
+        <v>474</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12661,7 +12788,7 @@
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>20</v>
@@ -12670,16 +12797,16 @@
         <v>20</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>513</v>
+        <v>167</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>514</v>
+        <v>168</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12706,11 +12833,13 @@
         <v>20</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>515</v>
+        <v>20</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>20</v>
@@ -12728,19 +12857,19 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>512</v>
+        <v>169</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>20</v>
@@ -12749,7 +12878,7 @@
         <v>20</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>20</v>
@@ -12757,21 +12886,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>534</v>
+        <v>475</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>535</v>
+        <v>475</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>20</v>
@@ -12783,15 +12912,17 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -12840,19 +12971,19 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>20</v>
@@ -12869,14 +13000,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>536</v>
+        <v>476</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>537</v>
+        <v>476</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>148</v>
+        <v>477</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12889,24 +13020,26 @@
         <v>20</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>174</v>
+        <v>478</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>175</v>
+        <v>479</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
       </c>
@@ -12942,19 +13075,19 @@
         <v>20</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>177</v>
+        <v>480</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12975,7 +13108,7 @@
         <v>20</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>20</v>
@@ -12983,10 +13116,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>481</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>539</v>
+        <v>481</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13009,20 +13142,18 @@
         <v>89</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>205</v>
+        <v>482</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>206</v>
+        <v>483</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>20</v>
       </c>
@@ -13046,13 +13177,13 @@
         <v>20</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>20</v>
+        <v>485</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>20</v>
+        <v>483</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>20</v>
+        <v>486</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>20</v>
@@ -13070,7 +13201,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>209</v>
+        <v>481</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13079,30 +13210,30 @@
         <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>20</v>
+        <v>487</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>20</v>
+        <v>488</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>210</v>
+        <v>489</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>211</v>
+        <v>490</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>540</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>541</v>
+        <v>491</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13125,13 +13256,13 @@
         <v>20</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>90</v>
+        <v>293</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>167</v>
+        <v>492</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>168</v>
+        <v>493</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13182,7 +13313,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>169</v>
+        <v>491</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13191,10 +13322,10 @@
         <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>20</v>
@@ -13203,29 +13334,29 @@
         <v>20</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>171</v>
+        <v>494</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>20</v>
+        <v>495</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>542</v>
+        <v>496</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>543</v>
+        <v>496</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>20</v>
@@ -13234,19 +13365,19 @@
         <v>20</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>135</v>
+        <v>497</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>174</v>
+        <v>498</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>175</v>
+        <v>499</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>151</v>
+        <v>500</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13284,51 +13415,51 @@
         <v>20</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>177</v>
+        <v>496</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>20</v>
+        <v>487</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>20</v>
+        <v>462</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>20</v>
+        <v>501</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>171</v>
+        <v>502</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>20</v>
+        <v>503</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>544</v>
+        <v>504</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13339,7 +13470,7 @@
         <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>20</v>
@@ -13351,20 +13482,16 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>102</v>
+        <v>505</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>218</v>
+        <v>506</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>20</v>
       </c>
@@ -13412,13 +13539,13 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>222</v>
+        <v>504</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>20</v>
@@ -13427,24 +13554,24 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>20</v>
+        <v>445</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>223</v>
+        <v>508</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>224</v>
+        <v>509</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>546</v>
+        <v>510</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>547</v>
+        <v>510</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13455,7 +13582,7 @@
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>20</v>
@@ -13464,19 +13591,19 @@
         <v>20</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>227</v>
+        <v>511</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>228</v>
+        <v>512</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>229</v>
+        <v>513</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>230</v>
+        <v>514</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13526,13 +13653,13 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>231</v>
+        <v>510</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>20</v>
@@ -13547,18 +13674,18 @@
         <v>20</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>232</v>
+        <v>133</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>233</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>548</v>
+        <v>515</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>549</v>
+        <v>515</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13566,7 +13693,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>88</v>
@@ -13578,27 +13705,27 @@
         <v>20</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>108</v>
+        <v>293</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>236</v>
+        <v>516</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>550</v>
+        <v>20</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>20</v>
@@ -13640,7 +13767,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>240</v>
+        <v>515</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13649,30 +13776,30 @@
         <v>88</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>20</v>
+        <v>519</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>20</v>
+        <v>520</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>242</v>
+        <v>521</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>243</v>
+        <v>522</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>551</v>
+        <v>523</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>552</v>
+        <v>523</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13692,21 +13819,19 @@
         <v>20</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>227</v>
+        <v>524</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>246</v>
+        <v>525</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>247</v>
+        <v>526</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>20</v>
       </c>
@@ -13754,7 +13879,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13763,7 +13888,7 @@
         <v>88</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>100</v>
@@ -13775,18 +13900,18 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>251</v>
+        <v>527</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13806,23 +13931,19 @@
         <v>20</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>254</v>
+        <v>524</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>255</v>
+        <v>529</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>20</v>
       </c>
@@ -13870,7 +13991,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>259</v>
+        <v>528</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13891,18 +14012,18 @@
         <v>20</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>261</v>
+        <v>531</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13922,23 +14043,21 @@
         <v>20</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>227</v>
+        <v>533</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>264</v>
+        <v>534</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>265</v>
+        <v>535</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>20</v>
       </c>
@@ -13986,7 +14105,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>268</v>
+        <v>532</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14001,28 +14120,28 @@
         <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>20</v>
+        <v>519</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>269</v>
+        <v>537</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>270</v>
+        <v>538</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>517</v>
+        <v>20</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14041,15 +14160,17 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>518</v>
+        <v>466</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -14074,29 +14195,29 @@
         <v>20</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>558</v>
+        <v>20</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14111,24 +14232,24 @@
         <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>523</v>
+        <v>20</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>524</v>
+        <v>20</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>525</v>
+        <v>20</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>526</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14139,7 +14260,7 @@
         <v>78</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>20</v>
@@ -14148,20 +14269,18 @@
         <v>20</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>431</v>
+        <v>227</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>560</v>
+        <v>167</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -14210,19 +14329,19 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>559</v>
+        <v>169</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>20</v>
@@ -14231,7 +14350,7 @@
         <v>20</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>563</v>
+        <v>171</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>20</v>
@@ -14239,21 +14358,21 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>564</v>
+        <v>545</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>564</v>
+        <v>545</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>20</v>
@@ -14265,15 +14384,17 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -14322,19 +14443,19 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>20</v>
@@ -14351,14 +14472,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>148</v>
+        <v>477</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14371,24 +14492,26 @@
         <v>20</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>174</v>
+        <v>478</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>175</v>
+        <v>479</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="O105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>20</v>
       </c>
@@ -14436,7 +14559,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>177</v>
+        <v>480</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14457,7 +14580,7 @@
         <v>20</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>20</v>
@@ -14465,14 +14588,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14485,26 +14608,22 @@
         <v>20</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>443</v>
+        <v>548</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>20</v>
       </c>
@@ -14528,13 +14647,11 @@
         <v>20</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>20</v>
+        <v>550</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>20</v>
@@ -14552,7 +14669,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>445</v>
+        <v>547</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14564,7 +14681,7 @@
         <v>20</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>20</v>
@@ -14573,7 +14690,7 @@
         <v>20</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>20</v>
@@ -14581,14 +14698,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -14607,13 +14724,13 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14640,11 +14757,13 @@
         <v>20</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>20</v>
@@ -14662,7 +14781,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14677,26 +14796,28 @@
         <v>100</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>523</v>
+        <v>558</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>524</v>
+        <v>559</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>574</v>
+        <v>561</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C108" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="D108" t="s" s="2">
         <v>20</v>
       </c>
@@ -14705,7 +14826,7 @@
         <v>78</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>20</v>
@@ -14714,18 +14835,20 @@
         <v>20</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>190</v>
+        <v>466</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>20</v>
@@ -14750,13 +14873,13 @@
         <v>20</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>578</v>
+        <v>20</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>579</v>
+        <v>20</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>20</v>
@@ -14774,7 +14897,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>575</v>
+        <v>539</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14795,18 +14918,18 @@
         <v>20</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>580</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>581</v>
+        <v>544</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14817,7 +14940,7 @@
         <v>78</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>20</v>
@@ -14829,17 +14952,15 @@
         <v>20</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>582</v>
+        <v>227</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>583</v>
+        <v>167</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>20</v>
@@ -14888,19 +15009,19 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>581</v>
+        <v>169</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>20</v>
@@ -14909,7 +15030,7 @@
         <v>20</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>586</v>
+        <v>171</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>20</v>
@@ -14917,14 +15038,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>587</v>
+        <v>545</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -14943,20 +15064,18 @@
         <v>20</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>588</v>
+        <v>174</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>589</v>
+        <v>175</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>20</v>
       </c>
@@ -14980,13 +15099,13 @@
         <v>20</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>592</v>
+        <v>20</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>593</v>
+        <v>20</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>20</v>
@@ -15004,7 +15123,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>587</v>
+        <v>177</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15016,7 +15135,7 @@
         <v>20</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>20</v>
@@ -15025,22 +15144,22 @@
         <v>20</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>594</v>
+        <v>171</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>595</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>596</v>
+        <v>567</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>596</v>
+        <v>546</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>20</v>
+        <v>477</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15053,22 +15172,26 @@
         <v>20</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>597</v>
+        <v>478</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
       </c>
@@ -15092,13 +15215,13 @@
         <v>20</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>599</v>
+        <v>20</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>600</v>
+        <v>20</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>20</v>
@@ -15116,7 +15239,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>596</v>
+        <v>480</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15128,7 +15251,7 @@
         <v>20</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>20</v>
@@ -15137,18 +15260,18 @@
         <v>20</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>601</v>
+        <v>133</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>602</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>603</v>
+        <v>568</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>603</v>
+        <v>547</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15168,20 +15291,18 @@
         <v>20</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>190</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>604</v>
+        <v>548</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>606</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -15206,13 +15327,11 @@
         <v>20</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>607</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>608</v>
+        <v>550</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>20</v>
@@ -15230,7 +15349,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>603</v>
+        <v>547</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15251,18 +15370,18 @@
         <v>20</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>609</v>
+        <v>20</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>610</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>611</v>
+        <v>569</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>611</v>
+        <v>570</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15285,17 +15404,15 @@
         <v>20</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>431</v>
+        <v>90</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>612</v>
+        <v>167</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>614</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>20</v>
@@ -15344,7 +15461,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>611</v>
+        <v>169</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15353,10 +15470,10 @@
         <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>20</v>
@@ -15365,7 +15482,7 @@
         <v>20</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>615</v>
+        <v>171</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>20</v>
@@ -15373,21 +15490,21 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>616</v>
+        <v>571</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>616</v>
+        <v>572</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>20</v>
@@ -15399,15 +15516,17 @@
         <v>20</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>20</v>
@@ -15444,31 +15563,31 @@
         <v>20</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>20</v>
@@ -15485,10 +15604,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>617</v>
+        <v>573</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>617</v>
+        <v>574</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15508,19 +15627,23 @@
         <v>20</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>136</v>
+        <v>205</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>20</v>
       </c>
@@ -15556,17 +15679,19 @@
         <v>20</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC115" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD115" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15578,7 +15703,7 @@
         <v>20</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>20</v>
@@ -15587,22 +15712,20 @@
         <v>20</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>20</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>618</v>
+        <v>575</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>20</v>
       </c>
@@ -15623,13 +15746,13 @@
         <v>20</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>620</v>
+        <v>90</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>621</v>
+        <v>167</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>622</v>
+        <v>168</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15680,19 +15803,19 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>20</v>
@@ -15701,7 +15824,7 @@
         <v>20</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>20</v>
@@ -15709,23 +15832,21 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>623</v>
+        <v>577</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>624</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>20</v>
@@ -15737,15 +15858,17 @@
         <v>20</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>625</v>
+        <v>135</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>626</v>
+        <v>174</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>20</v>
@@ -15782,16 +15905,16 @@
         <v>20</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="AF117" t="s" s="2">
         <v>177</v>
@@ -15815,7 +15938,7 @@
         <v>20</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>20</v>
@@ -15823,45 +15946,45 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>628</v>
+        <v>579</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>628</v>
+        <v>580</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J118" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>443</v>
+        <v>218</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>444</v>
+        <v>219</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>20</v>
@@ -15910,19 +16033,19 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>445</v>
+        <v>222</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>20</v>
@@ -15931,18 +16054,18 @@
         <v>20</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>133</v>
+        <v>223</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>629</v>
+        <v>581</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>629</v>
+        <v>582</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15962,18 +16085,20 @@
         <v>20</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>630</v>
+        <v>228</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>20</v>
@@ -16022,7 +16147,7 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>629</v>
+        <v>231</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16043,18 +16168,18 @@
         <v>20</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>632</v>
+        <v>233</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>633</v>
+        <v>583</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>633</v>
+        <v>584</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16062,7 +16187,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>88</v>
@@ -16074,25 +16199,27 @@
         <v>20</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>331</v>
+        <v>108</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>634</v>
+        <v>236</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>635</v>
+        <v>237</v>
       </c>
       <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+      <c r="O120" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>20</v>
+        <v>585</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>20</v>
@@ -16134,7 +16261,7 @@
         <v>20</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>633</v>
+        <v>240</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16143,7 +16270,7 @@
         <v>88</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>100</v>
@@ -16155,18 +16282,18 @@
         <v>20</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>636</v>
+        <v>242</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>637</v>
+        <v>586</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>637</v>
+        <v>587</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16186,19 +16313,21 @@
         <v>20</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>638</v>
+        <v>246</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>639</v>
+        <v>247</v>
       </c>
       <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+      <c r="O121" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>20</v>
       </c>
@@ -16222,13 +16351,13 @@
         <v>20</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>640</v>
+        <v>20</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>641</v>
+        <v>20</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>20</v>
@@ -16246,7 +16375,7 @@
         <v>20</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>637</v>
+        <v>249</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16255,7 +16384,7 @@
         <v>88</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>100</v>
@@ -16267,18 +16396,18 @@
         <v>20</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>642</v>
+        <v>250</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>643</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>644</v>
+        <v>588</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>644</v>
+        <v>589</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16298,19 +16427,23 @@
         <v>20</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>190</v>
+        <v>254</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>645</v>
+        <v>255</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>20</v>
       </c>
@@ -16334,13 +16467,13 @@
         <v>20</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>647</v>
+        <v>20</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>648</v>
+        <v>20</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>20</v>
@@ -16358,7 +16491,7 @@
         <v>20</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>644</v>
+        <v>259</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16379,18 +16512,18 @@
         <v>20</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>171</v>
+        <v>260</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>649</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>650</v>
+        <v>590</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>650</v>
+        <v>591</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16410,19 +16543,23 @@
         <v>20</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>331</v>
+        <v>227</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>651</v>
+        <v>264</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>20</v>
       </c>
@@ -16470,7 +16607,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>650</v>
+        <v>268</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16491,29 +16628,29 @@
         <v>20</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>653</v>
+        <v>269</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>654</v>
+        <v>270</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>655</v>
+        <v>592</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>20</v>
+        <v>552</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>20</v>
@@ -16522,16 +16659,16 @@
         <v>20</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>190</v>
+        <v>553</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>656</v>
+        <v>554</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>657</v>
+        <v>555</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16562,7 +16699,7 @@
       </c>
       <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>658</v>
+        <v>593</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>20</v>
@@ -16580,13 +16717,13 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>655</v>
+        <v>551</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>20</v>
@@ -16595,24 +16732,24 @@
         <v>100</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>20</v>
+        <v>558</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>20</v>
+        <v>559</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>659</v>
+        <v>560</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>660</v>
+        <v>561</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>661</v>
+        <v>594</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>661</v>
+        <v>594</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16632,19 +16769,19 @@
         <v>20</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>431</v>
+        <v>466</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>662</v>
+        <v>595</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>663</v>
+        <v>596</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>664</v>
+        <v>597</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16694,7 +16831,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>661</v>
+        <v>594</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16715,7 +16852,7 @@
         <v>20</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>665</v>
+        <v>598</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>20</v>
@@ -16723,10 +16860,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>666</v>
+        <v>599</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>666</v>
+        <v>599</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16835,10 +16972,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>667</v>
+        <v>600</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>667</v>
+        <v>600</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16949,14 +17086,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>668</v>
+        <v>601</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>668</v>
+        <v>601</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16978,10 +17115,10 @@
         <v>135</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>151</v>
@@ -17036,7 +17173,7 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17065,21 +17202,21 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>669</v>
+        <v>602</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>669</v>
+        <v>602</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>20</v>
+        <v>603</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>20</v>
@@ -17088,16 +17225,16 @@
         <v>20</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>670</v>
+        <v>604</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>671</v>
+        <v>605</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>672</v>
+        <v>606</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17124,13 +17261,11 @@
         <v>20</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>20</v>
+        <v>607</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>20</v>
@@ -17148,13 +17283,13 @@
         <v>20</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>669</v>
+        <v>602</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>20</v>
@@ -17163,24 +17298,24 @@
         <v>100</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>673</v>
+        <v>558</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>674</v>
+        <v>559</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>467</v>
+        <v>608</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>675</v>
+        <v>609</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>676</v>
+        <v>610</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>676</v>
+        <v>610</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17191,7 +17326,7 @@
         <v>78</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>20</v>
@@ -17203,17 +17338,15 @@
         <v>20</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>108</v>
+        <v>190</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>677</v>
+        <v>611</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>679</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>20</v>
@@ -17241,10 +17374,10 @@
         <v>112</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>680</v>
+        <v>613</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>681</v>
+        <v>614</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>20</v>
@@ -17262,13 +17395,13 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>676</v>
+        <v>610</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>20</v>
@@ -17283,18 +17416,18 @@
         <v>20</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>682</v>
+        <v>171</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>20</v>
+        <v>615</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>683</v>
+        <v>616</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>683</v>
+        <v>616</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17305,7 +17438,7 @@
         <v>78</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>20</v>
@@ -17317,16 +17450,16 @@
         <v>20</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>190</v>
+        <v>617</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>684</v>
+        <v>618</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>685</v>
+        <v>619</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>686</v>
+        <v>620</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17352,13 +17485,13 @@
         <v>20</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>687</v>
+        <v>20</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>688</v>
+        <v>20</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>20</v>
@@ -17376,13 +17509,13 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>683</v>
+        <v>616</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>20</v>
@@ -17397,7 +17530,7 @@
         <v>20</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>20</v>
+        <v>621</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>20</v>
@@ -17405,10 +17538,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>689</v>
+        <v>622</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>689</v>
+        <v>622</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17419,7 +17552,7 @@
         <v>78</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>20</v>
@@ -17431,16 +17564,20 @@
         <v>20</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>293</v>
+        <v>190</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>690</v>
+        <v>623</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
+        <v>624</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
       </c>
@@ -17464,13 +17601,13 @@
         <v>20</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>20</v>
+        <v>627</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>20</v>
+        <v>628</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>20</v>
@@ -17488,13 +17625,13 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>689</v>
+        <v>622</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>20</v>
@@ -17509,9 +17646,2493 @@
         <v>20</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>459</v>
+        <v>629</v>
       </c>
       <c r="AN132" t="s" s="2">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC137" s="2"/>
+      <c r="AD137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="D138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="D139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="P140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
+      <c r="P143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" s="2"/>
+      <c r="P144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y146" s="2"/>
+      <c r="Z146" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="P150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AN154" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -624,7 +624,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/hl7-at-patientidentifier</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0203</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1937,7 +1937,7 @@
     <t>Code für den Typ der LKF Diagnose, der angibt ob es sich um eine Haupt- oder Nebendiagnose handelt</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-lkf-diagnose-typ.html</t>
+    <t>https://termgit.elga.gv.at/CodeSystem-lkf-diagnose-typ.html</t>
   </si>
   <si>
     <t>DG1-6 (Diagnosis Type)</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-12T14:30:40+00:00</t>
+    <t>2024-12-13T08:39:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA (https://www.elga.gv.at/)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1182,49 +1182,49 @@
     <t>Encounter.class.text</t>
   </si>
   <si>
-    <t>Encounter.class:Aufnahmeart</t>
-  </si>
-  <si>
-    <t>Aufnahmeart</t>
-  </si>
-  <si>
-    <t>http://example.org/ValueSet/moped-aufnahmeart-valueset</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.id</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.extension</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.system</t>
+    <t>Encounter.class:Aufnahmeart2</t>
+  </si>
+  <si>
+    <t>Aufnahmeart2</t>
+  </si>
+  <si>
+    <t>http://example.org/ValueSet/moped-aufnahmeart2-valueset</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.system</t>
   </si>
   <si>
     <t>http://tbd.at/moped-ext-aufnahmeart</t>
   </si>
   <si>
-    <t>Encounter.class:Aufnahmeart.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.code</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.display</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.text</t>
+    <t>Encounter.class:Aufnahmeart2.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.code</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.text</t>
   </si>
   <si>
     <t>Encounter.priority</t>
@@ -2063,20 +2063,20 @@
     <t>Encounter.admission.extension</t>
   </si>
   <si>
-    <t>Encounter.admission.extension:zugangsart</t>
-  </si>
-  <si>
-    <t>zugangsart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-zugangsart}
+    <t>Encounter.admission.extension:aufnahmeart</t>
+  </si>
+  <si>
+    <t>aufnahmeart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-aufnahmeart}
 </t>
   </si>
   <si>
-    <t>Zugangsart</t>
-  </si>
-  <si>
-    <t>MOPED Extension für die Art des Zugangs.</t>
+    <t>Aufnahmeart</t>
+  </si>
+  <si>
+    <t>MOPED Extension für die Aufnahmeart.</t>
   </si>
   <si>
     <t>Encounter.admission.extension:transportart</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounterBund.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
